--- a/backend/data/vehicle_pricing_sample.xlsx
+++ b/backend/data/vehicle_pricing_sample.xlsx
@@ -32,7 +32,7 @@
     <t xml:space="preserve">vehicle_type_id</t>
   </si>
   <si>
-    <t xml:space="preserve">price_k</t>
+    <t xml:space="preserve">price_uzs</t>
   </si>
   <si>
     <t xml:space="preserve">srv-1</t>
@@ -224,13 +224,13 @@
     <t xml:space="preserve">Usta Top vehicle pricing template</t>
   </si>
   <si>
-    <t xml:space="preserve">1. pricing_matrix sheet ichida price_k ustunini o‘zgartiring.</t>
+    <t xml:space="preserve">1. pricing_matrix sheet ichida price_uzs ustunini to‘liq UZS qiymatida o‘zgartiring.</t>
   </si>
   <si>
     <t xml:space="preserve">2. catalog_vehicle_id bo‘sh bo‘lsa, brand + model + vehicle_type_id ni to‘ldirib custom model qo‘shishingiz mumkin.</t>
   </si>
   <si>
-    <t xml:space="preserve">3. service_id va price_k majburiy. Narxlar ming so‘m formatida saqlanadi.</t>
+    <t xml:space="preserve">3. service_id va price_uzs majburiy. Masalan: 100000 yoki 150000 UZS.</t>
   </si>
 </sst>
 </file>
@@ -518,7 +518,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="3">
@@ -541,7 +541,7 @@
         <v>15</v>
       </c>
       <c r="G3" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="4">
@@ -564,7 +564,7 @@
         <v>18</v>
       </c>
       <c r="G4" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="5">
@@ -587,7 +587,7 @@
         <v>12</v>
       </c>
       <c r="G5" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="6">
@@ -610,7 +610,7 @@
         <v>12</v>
       </c>
       <c r="G6" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="7">
@@ -633,7 +633,7 @@
         <v>12</v>
       </c>
       <c r="G7" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="8">
@@ -656,7 +656,7 @@
         <v>27</v>
       </c>
       <c r="G8" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="9">
@@ -679,7 +679,7 @@
         <v>12</v>
       </c>
       <c r="G9" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="10">
@@ -702,7 +702,7 @@
         <v>12</v>
       </c>
       <c r="G10" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="11">
@@ -725,7 +725,7 @@
         <v>34</v>
       </c>
       <c r="G11" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="12">
@@ -748,7 +748,7 @@
         <v>27</v>
       </c>
       <c r="G12" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="13">
@@ -771,7 +771,7 @@
         <v>12</v>
       </c>
       <c r="G13" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="14">
@@ -794,7 +794,7 @@
         <v>42</v>
       </c>
       <c r="G14" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="15">
@@ -817,7 +817,7 @@
         <v>12</v>
       </c>
       <c r="G15" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="16">
@@ -840,7 +840,7 @@
         <v>42</v>
       </c>
       <c r="G16" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="17">
@@ -863,7 +863,7 @@
         <v>42</v>
       </c>
       <c r="G17" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="18">
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
       <c r="G18" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="19">
@@ -909,7 +909,7 @@
         <v>12</v>
       </c>
       <c r="G19" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="20">
@@ -932,7 +932,7 @@
         <v>42</v>
       </c>
       <c r="G20" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="21">
@@ -955,7 +955,7 @@
         <v>18</v>
       </c>
       <c r="G21" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="22">
@@ -978,7 +978,7 @@
         <v>18</v>
       </c>
       <c r="G22" s="2">
-        <v>120</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="23">
@@ -1001,7 +1001,7 @@
         <v>12</v>
       </c>
       <c r="G23" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="24">
@@ -1024,7 +1024,7 @@
         <v>15</v>
       </c>
       <c r="G24" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="25">
@@ -1047,7 +1047,7 @@
         <v>18</v>
       </c>
       <c r="G25" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="26">
@@ -1070,7 +1070,7 @@
         <v>12</v>
       </c>
       <c r="G26" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="27">
@@ -1093,7 +1093,7 @@
         <v>12</v>
       </c>
       <c r="G27" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="28">
@@ -1116,7 +1116,7 @@
         <v>12</v>
       </c>
       <c r="G28" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="29">
@@ -1139,7 +1139,7 @@
         <v>27</v>
       </c>
       <c r="G29" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="30">
@@ -1162,7 +1162,7 @@
         <v>12</v>
       </c>
       <c r="G30" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="31">
@@ -1185,7 +1185,7 @@
         <v>12</v>
       </c>
       <c r="G31" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="32">
@@ -1208,7 +1208,7 @@
         <v>34</v>
       </c>
       <c r="G32" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="33">
@@ -1231,7 +1231,7 @@
         <v>27</v>
       </c>
       <c r="G33" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="34">
@@ -1254,7 +1254,7 @@
         <v>12</v>
       </c>
       <c r="G34" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="35">
@@ -1277,7 +1277,7 @@
         <v>42</v>
       </c>
       <c r="G35" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="36">
@@ -1300,7 +1300,7 @@
         <v>12</v>
       </c>
       <c r="G36" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="37">
@@ -1323,7 +1323,7 @@
         <v>42</v>
       </c>
       <c r="G37" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="38">
@@ -1346,7 +1346,7 @@
         <v>42</v>
       </c>
       <c r="G38" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="39">
@@ -1369,7 +1369,7 @@
         <v>12</v>
       </c>
       <c r="G39" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="40">
@@ -1392,7 +1392,7 @@
         <v>12</v>
       </c>
       <c r="G40" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="41">
@@ -1415,7 +1415,7 @@
         <v>42</v>
       </c>
       <c r="G41" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="42">
@@ -1438,7 +1438,7 @@
         <v>18</v>
       </c>
       <c r="G42" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="43">
@@ -1461,7 +1461,7 @@
         <v>18</v>
       </c>
       <c r="G43" s="2">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="44">
@@ -1484,7 +1484,7 @@
         <v>12</v>
       </c>
       <c r="G44" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="45">
@@ -1507,7 +1507,7 @@
         <v>15</v>
       </c>
       <c r="G45" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="46">
@@ -1530,7 +1530,7 @@
         <v>18</v>
       </c>
       <c r="G46" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="47">
@@ -1553,7 +1553,7 @@
         <v>12</v>
       </c>
       <c r="G47" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="48">
@@ -1576,7 +1576,7 @@
         <v>12</v>
       </c>
       <c r="G48" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="49">
@@ -1599,7 +1599,7 @@
         <v>12</v>
       </c>
       <c r="G49" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="50">
@@ -1622,7 +1622,7 @@
         <v>27</v>
       </c>
       <c r="G50" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="51">
@@ -1645,7 +1645,7 @@
         <v>12</v>
       </c>
       <c r="G51" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="52">
@@ -1668,7 +1668,7 @@
         <v>12</v>
       </c>
       <c r="G52" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="53">
@@ -1691,7 +1691,7 @@
         <v>34</v>
       </c>
       <c r="G53" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="54">
@@ -1714,7 +1714,7 @@
         <v>27</v>
       </c>
       <c r="G54" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="55">
@@ -1737,7 +1737,7 @@
         <v>12</v>
       </c>
       <c r="G55" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="56">
@@ -1760,7 +1760,7 @@
         <v>42</v>
       </c>
       <c r="G56" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="57">
@@ -1783,7 +1783,7 @@
         <v>12</v>
       </c>
       <c r="G57" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="58">
@@ -1806,7 +1806,7 @@
         <v>42</v>
       </c>
       <c r="G58" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="59">
@@ -1829,7 +1829,7 @@
         <v>42</v>
       </c>
       <c r="G59" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="60">
@@ -1852,7 +1852,7 @@
         <v>12</v>
       </c>
       <c r="G60" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="61">
@@ -1875,7 +1875,7 @@
         <v>12</v>
       </c>
       <c r="G61" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="62">
@@ -1898,7 +1898,7 @@
         <v>42</v>
       </c>
       <c r="G62" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="63">
@@ -1921,7 +1921,7 @@
         <v>18</v>
       </c>
       <c r="G63" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="64">
@@ -1944,7 +1944,7 @@
         <v>18</v>
       </c>
       <c r="G64" s="2">
-        <v>180</v>
+        <v>180000</v>
       </c>
     </row>
   </sheetData>
